--- a/95 Файлы/Допуск. Сириус Арена/Допуск. Сириус Арена. Монтажлифтсервис.xlsx
+++ b/95 Файлы/Допуск. Сириус Арена/Допуск. Сириус Арена. Монтажлифтсервис.xlsx
@@ -171,7 +171,7 @@
     <t>0325№234112</t>
   </si>
   <si>
-    <t>с 1.04.2026г. по 30.04.2026г.</t>
+    <t>с 1.05.2026г. по 31.05.2026г.</t>
   </si>
 </sst>
 </file>
@@ -364,53 +364,53 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -721,125 +721,125 @@
       </c>
     </row>
     <row r="2" spans="2:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
     </row>
     <row r="3" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="F3" s="22" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="F3" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
     </row>
     <row r="4" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
     </row>
     <row r="5" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="F5" s="20" t="s">
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="F5" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
     </row>
     <row r="6" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="7" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
     </row>
     <row r="8" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
     </row>
     <row r="9" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="F9" s="20" t="s">
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="F9" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
     </row>
     <row r="10" spans="2:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
     </row>
     <row r="11" spans="2:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
@@ -851,18 +851,18 @@
       <c r="D11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26" t="s">
+      <c r="F11" s="31"/>
+      <c r="G11" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26" t="s">
+      <c r="H11" s="31"/>
+      <c r="I11" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="26"/>
+      <c r="J11" s="31"/>
     </row>
     <row r="12" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="12">
@@ -897,18 +897,18 @@
       <c r="D13" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="27"/>
+      <c r="F13" s="21"/>
       <c r="G13" s="28" t="s">
         <v>48</v>
       </c>
       <c r="H13" s="28"/>
-      <c r="I13" s="27" t="s">
+      <c r="I13" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="27"/>
+      <c r="J13" s="21"/>
     </row>
     <row r="14" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="13">
@@ -920,18 +920,18 @@
       <c r="D14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="27"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="28" t="s">
         <v>49</v>
       </c>
       <c r="H14" s="28"/>
-      <c r="I14" s="27" t="s">
+      <c r="I14" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="27"/>
+      <c r="J14" s="21"/>
     </row>
     <row r="15" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="13">
@@ -943,18 +943,18 @@
       <c r="D15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="29"/>
-      <c r="G15" s="30" t="s">
+      <c r="F15" s="19"/>
+      <c r="G15" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="27" t="s">
+      <c r="H15" s="20"/>
+      <c r="I15" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="J15" s="27"/>
+      <c r="J15" s="21"/>
     </row>
     <row r="16" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="12">
@@ -1003,47 +1003,47 @@
       </c>
     </row>
     <row r="18" spans="2:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="23" t="s">
+      <c r="H18" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
     </row>
     <row r="19" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="25" t="s">
+      <c r="H19" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
     </row>
     <row r="20" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="34">
+      <c r="B20" s="27">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
-      </c>
-      <c r="C20" s="34"/>
+        <v>46140</v>
+      </c>
+      <c r="C20" s="27"/>
     </row>
     <row r="21" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="31"/>
+      <c r="C21" s="22"/>
     </row>
     <row r="22" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1054,6 +1054,31 @@
     <row r="28" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="I15:J15"/>
@@ -1063,31 +1088,6 @@
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:J4"/>
   </mergeCells>
   <pageMargins left="0.31535433070866109" right="0.31535433070866109" top="0.94527559055118116" bottom="0.94527559055118116" header="0.55157480314960605" footer="0.55157480314960605"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
